--- a/project/outputs_xlsx_solution/test_new3.4-wide-NR-4.xlsx
+++ b/project/outputs_xlsx_solution/test_new3.4-wide-NR-4.xlsx
@@ -666,9 +666,6 @@
       <c r="AW1">
         <v>46</v>
       </c>
-      <c r="AX1">
-        <v>47</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -826,7 +823,7 @@
         <v>21</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="I7" t="s">
         <v>14</v>
@@ -835,9 +832,6 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" t="s">
         <v>20</v>
       </c>
     </row>
@@ -861,7 +855,7 @@
         <v>21</v>
       </c>
       <c r="I8" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J8" t="s">
         <v>14</v>
@@ -870,9 +864,6 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -898,6 +889,9 @@
       <c r="J9" t="s">
         <v>26</v>
       </c>
+      <c r="L9" t="s">
+        <v>14</v>
+      </c>
       <c r="M9" t="s">
         <v>14</v>
       </c>
@@ -908,9 +902,6 @@
         <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -931,7 +922,7 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K10" t="s">
         <v>14</v>
@@ -940,12 +931,9 @@
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" t="s">
         <v>19</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="P10" t="s">
         <v>20</v>
       </c>
     </row>
@@ -969,11 +957,11 @@
         <v>27</v>
       </c>
       <c r="K11" t="s">
-        <v>27</v>
-      </c>
-      <c r="L11" t="s">
         <v>26</v>
       </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
       <c r="N11" t="s">
         <v>14</v>
       </c>
@@ -981,9 +969,6 @@
         <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1003,12 +988,15 @@
       <c r="G12" t="s">
         <v>9</v>
       </c>
+      <c r="K12" t="s">
+        <v>21</v>
+      </c>
       <c r="L12" t="s">
-        <v>21</v>
-      </c>
-      <c r="M12" t="s">
         <v>26</v>
       </c>
+      <c r="P12" t="s">
+        <v>14</v>
+      </c>
       <c r="Q12" t="s">
         <v>14</v>
       </c>
@@ -1019,9 +1007,6 @@
         <v>14</v>
       </c>
       <c r="T12" t="s">
-        <v>14</v>
-      </c>
-      <c r="U12" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1041,6 +1026,9 @@
       <c r="G13" t="s">
         <v>9</v>
       </c>
+      <c r="L13" t="s">
+        <v>21</v>
+      </c>
       <c r="M13" t="s">
         <v>21</v>
       </c>
@@ -1051,15 +1039,12 @@
         <v>21</v>
       </c>
       <c r="P13" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q13" t="s">
-        <v>14</v>
-      </c>
-      <c r="R13" t="s">
         <v>19</v>
       </c>
-      <c r="U13" t="s">
+      <c r="T13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1079,13 +1064,13 @@
       <c r="H14" t="s">
         <v>9</v>
       </c>
+      <c r="P14" t="s">
+        <v>14</v>
+      </c>
       <c r="Q14" t="s">
-        <v>14</v>
-      </c>
-      <c r="R14" t="s">
         <v>19</v>
       </c>
-      <c r="U14" t="s">
+      <c r="T14" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1105,16 +1090,16 @@
       <c r="H15" t="s">
         <v>9</v>
       </c>
+      <c r="P15" t="s">
+        <v>15</v>
+      </c>
       <c r="Q15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R15" t="s">
-        <v>14</v>
-      </c>
-      <c r="S15" t="s">
         <v>19</v>
       </c>
-      <c r="U15" t="s">
+      <c r="T15" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1134,6 +1119,9 @@
       <c r="H16" t="s">
         <v>9</v>
       </c>
+      <c r="P16" t="s">
+        <v>21</v>
+      </c>
       <c r="Q16" t="s">
         <v>21</v>
       </c>
@@ -1144,12 +1132,9 @@
         <v>21</v>
       </c>
       <c r="T16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U16" t="s">
-        <v>14</v>
-      </c>
-      <c r="V16" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1169,13 +1154,13 @@
       <c r="H17" t="s">
         <v>9</v>
       </c>
+      <c r="T17" t="s">
+        <v>26</v>
+      </c>
       <c r="U17" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="V17" t="s">
-        <v>14</v>
-      </c>
-      <c r="W17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1189,11 +1174,14 @@
       <c r="C18" t="s">
         <v>17</v>
       </c>
+      <c r="V18" t="s">
+        <v>5</v>
+      </c>
       <c r="W18" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X18" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="s">
         <v>14</v>
@@ -1202,9 +1190,6 @@
         <v>14</v>
       </c>
       <c r="AA18" t="s">
-        <v>14</v>
-      </c>
-      <c r="AB18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1218,11 +1203,14 @@
       <c r="C19" t="s">
         <v>13</v>
       </c>
+      <c r="V19" t="s">
+        <v>5</v>
+      </c>
       <c r="W19" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X19" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y19" t="s">
         <v>14</v>
@@ -1234,9 +1222,6 @@
         <v>14</v>
       </c>
       <c r="AB19" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC19" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1250,19 +1235,19 @@
       <c r="C20" t="s">
         <v>18</v>
       </c>
+      <c r="V20" t="s">
+        <v>5</v>
+      </c>
       <c r="W20" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X20" t="s">
-        <v>9</v>
-      </c>
-      <c r="Y20" t="s">
         <v>26</v>
       </c>
+      <c r="AA20" t="s">
+        <v>14</v>
+      </c>
       <c r="AB20" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1276,19 +1261,19 @@
       <c r="C21" t="s">
         <v>22</v>
       </c>
+      <c r="V21" t="s">
+        <v>5</v>
+      </c>
       <c r="W21" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="X21" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z21" t="s">
         <v>19</v>
       </c>
-      <c r="AC21" t="s">
+      <c r="AB21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1302,22 +1287,22 @@
       <c r="C22" t="s">
         <v>23</v>
       </c>
+      <c r="W22" t="s">
+        <v>5</v>
+      </c>
       <c r="X22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Y22" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="Z22" t="s">
         <v>21</v>
       </c>
       <c r="AA22" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AB22" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC22" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1331,19 +1316,19 @@
       <c r="C23" t="s">
         <v>24</v>
       </c>
+      <c r="W23" t="s">
+        <v>5</v>
+      </c>
       <c r="X23" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>21</v>
       </c>
       <c r="AB23" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AC23" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD23" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1357,19 +1342,19 @@
       <c r="C24" t="s">
         <v>25</v>
       </c>
+      <c r="W24" t="s">
+        <v>5</v>
+      </c>
       <c r="X24" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>26</v>
       </c>
       <c r="AC24" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AD24" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1383,11 +1368,14 @@
       <c r="C25" t="s">
         <v>17</v>
       </c>
+      <c r="X25" t="s">
+        <v>5</v>
+      </c>
       <c r="Y25" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>14</v>
       </c>
       <c r="AC25" t="s">
         <v>14</v>
@@ -1396,9 +1384,6 @@
         <v>14</v>
       </c>
       <c r="AE25" t="s">
-        <v>14</v>
-      </c>
-      <c r="AF25" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1412,11 +1397,14 @@
       <c r="C26" t="s">
         <v>13</v>
       </c>
+      <c r="X26" t="s">
+        <v>5</v>
+      </c>
       <c r="Y26" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>14</v>
       </c>
       <c r="AC26" t="s">
         <v>14</v>
@@ -1428,9 +1416,6 @@
         <v>14</v>
       </c>
       <c r="AF26" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG26" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1444,19 +1429,19 @@
       <c r="C27" t="s">
         <v>18</v>
       </c>
+      <c r="X27" t="s">
+        <v>5</v>
+      </c>
       <c r="Y27" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>9</v>
-      </c>
-      <c r="AD27" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC27" t="s">
         <v>26</v>
       </c>
+      <c r="AE27" t="s">
+        <v>14</v>
+      </c>
       <c r="AF27" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG27" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1470,22 +1455,22 @@
       <c r="C28" t="s">
         <v>22</v>
       </c>
+      <c r="X28" t="s">
+        <v>5</v>
+      </c>
       <c r="Y28" t="s">
-        <v>5</v>
-      </c>
-      <c r="Z28" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>21</v>
       </c>
       <c r="AD28" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AF28" t="s">
-        <v>19</v>
-      </c>
-      <c r="AG28" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1499,19 +1484,19 @@
       <c r="C29" t="s">
         <v>23</v>
       </c>
+      <c r="Y29" t="s">
+        <v>5</v>
+      </c>
       <c r="Z29" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AD29" t="s">
+        <v>21</v>
       </c>
       <c r="AE29" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AF29" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG29" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1525,19 +1510,19 @@
       <c r="C30" t="s">
         <v>24</v>
       </c>
+      <c r="Y30" t="s">
+        <v>5</v>
+      </c>
       <c r="Z30" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>21</v>
       </c>
       <c r="AF30" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH30" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1551,19 +1536,19 @@
       <c r="C31" t="s">
         <v>25</v>
       </c>
+      <c r="Y31" t="s">
+        <v>5</v>
+      </c>
       <c r="Z31" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>26</v>
       </c>
       <c r="AG31" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AH31" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI31" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1577,11 +1562,14 @@
       <c r="C32" t="s">
         <v>17</v>
       </c>
+      <c r="Z32" t="s">
+        <v>5</v>
+      </c>
       <c r="AA32" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>14</v>
       </c>
       <c r="AG32" t="s">
         <v>14</v>
@@ -1590,9 +1578,6 @@
         <v>14</v>
       </c>
       <c r="AI32" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ32" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1606,11 +1591,14 @@
       <c r="C33" t="s">
         <v>13</v>
       </c>
+      <c r="Z33" t="s">
+        <v>5</v>
+      </c>
       <c r="AA33" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB33" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AF33" t="s">
+        <v>14</v>
       </c>
       <c r="AG33" t="s">
         <v>14</v>
@@ -1622,9 +1610,6 @@
         <v>14</v>
       </c>
       <c r="AJ33" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK33" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1638,19 +1623,19 @@
       <c r="C34" t="s">
         <v>18</v>
       </c>
+      <c r="Z34" t="s">
+        <v>5</v>
+      </c>
       <c r="AA34" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB34" t="s">
-        <v>9</v>
-      </c>
-      <c r="AH34" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG34" t="s">
         <v>26</v>
       </c>
+      <c r="AI34" t="s">
+        <v>14</v>
+      </c>
       <c r="AJ34" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK34" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1664,22 +1649,22 @@
       <c r="C35" t="s">
         <v>22</v>
       </c>
+      <c r="Z35" t="s">
+        <v>5</v>
+      </c>
       <c r="AA35" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB35" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AG35" t="s">
+        <v>21</v>
       </c>
       <c r="AH35" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AI35" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AJ35" t="s">
-        <v>19</v>
-      </c>
-      <c r="AK35" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1693,19 +1678,19 @@
       <c r="C36" t="s">
         <v>23</v>
       </c>
+      <c r="AA36" t="s">
+        <v>5</v>
+      </c>
       <c r="AB36" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC36" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>21</v>
       </c>
       <c r="AI36" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AJ36" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK36" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1719,19 +1704,19 @@
       <c r="C37" t="s">
         <v>24</v>
       </c>
+      <c r="AA37" t="s">
+        <v>5</v>
+      </c>
       <c r="AB37" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC37" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>21</v>
       </c>
       <c r="AJ37" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AK37" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL37" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1745,19 +1730,19 @@
       <c r="C38" t="s">
         <v>25</v>
       </c>
+      <c r="AA38" t="s">
+        <v>5</v>
+      </c>
       <c r="AB38" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC38" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AJ38" t="s">
+        <v>26</v>
       </c>
       <c r="AK38" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AL38" t="s">
-        <v>14</v>
-      </c>
-      <c r="AM38" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1771,11 +1756,14 @@
       <c r="C39" t="s">
         <v>17</v>
       </c>
+      <c r="AB39" t="s">
+        <v>5</v>
+      </c>
       <c r="AC39" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD39" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AJ39" t="s">
+        <v>14</v>
       </c>
       <c r="AK39" t="s">
         <v>14</v>
@@ -1784,9 +1772,6 @@
         <v>14</v>
       </c>
       <c r="AM39" t="s">
-        <v>14</v>
-      </c>
-      <c r="AN39" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1800,11 +1785,14 @@
       <c r="C40" t="s">
         <v>13</v>
       </c>
+      <c r="AB40" t="s">
+        <v>5</v>
+      </c>
       <c r="AC40" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD40" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AJ40" t="s">
+        <v>14</v>
       </c>
       <c r="AK40" t="s">
         <v>14</v>
@@ -1816,9 +1804,6 @@
         <v>14</v>
       </c>
       <c r="AN40" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO40" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1832,19 +1817,19 @@
       <c r="C41" t="s">
         <v>18</v>
       </c>
+      <c r="AB41" t="s">
+        <v>5</v>
+      </c>
       <c r="AC41" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD41" t="s">
-        <v>9</v>
-      </c>
-      <c r="AL41" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK41" t="s">
         <v>26</v>
       </c>
+      <c r="AM41" t="s">
+        <v>14</v>
+      </c>
       <c r="AN41" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO41" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1858,22 +1843,22 @@
       <c r="C42" t="s">
         <v>22</v>
       </c>
+      <c r="AB42" t="s">
+        <v>5</v>
+      </c>
       <c r="AC42" t="s">
-        <v>5</v>
-      </c>
-      <c r="AD42" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AK42" t="s">
+        <v>21</v>
       </c>
       <c r="AL42" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AM42" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AN42" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO42" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1887,19 +1872,19 @@
       <c r="C43" t="s">
         <v>23</v>
       </c>
+      <c r="AC43" t="s">
+        <v>5</v>
+      </c>
       <c r="AD43" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AL43" t="s">
+        <v>21</v>
       </c>
       <c r="AM43" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AN43" t="s">
-        <v>14</v>
-      </c>
-      <c r="AO43" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1913,19 +1898,19 @@
       <c r="C44" t="s">
         <v>24</v>
       </c>
+      <c r="AC44" t="s">
+        <v>5</v>
+      </c>
       <c r="AD44" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="AM44" t="s">
+        <v>21</v>
       </c>
       <c r="AN44" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AO44" t="s">
-        <v>14</v>
-      </c>
-      <c r="AP44" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1939,19 +1924,19 @@
       <c r="C45" t="s">
         <v>25</v>
       </c>
-      <c r="AD45" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF45" t="s">
-        <v>9</v>
+      <c r="AC45" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN45" t="s">
+        <v>26</v>
       </c>
       <c r="AO45" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AP45" t="s">
-        <v>14</v>
-      </c>
-      <c r="AQ45" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1965,11 +1950,14 @@
       <c r="C46" t="s">
         <v>28</v>
       </c>
+      <c r="AP46" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ46" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AR46" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AS46" t="s">
         <v>14</v>
@@ -1978,9 +1966,6 @@
         <v>14</v>
       </c>
       <c r="AU46" t="s">
-        <v>14</v>
-      </c>
-      <c r="AV46" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1994,11 +1979,14 @@
       <c r="C47" t="s">
         <v>13</v>
       </c>
+      <c r="AP47" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ47" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AR47" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AS47" t="s">
         <v>14</v>
@@ -2010,9 +1998,6 @@
         <v>14</v>
       </c>
       <c r="AV47" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW47" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2026,19 +2011,19 @@
       <c r="C48" t="s">
         <v>29</v>
       </c>
+      <c r="AP48" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AR48" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS48" t="s">
         <v>26</v>
       </c>
+      <c r="AU48" t="s">
+        <v>14</v>
+      </c>
       <c r="AV48" t="s">
-        <v>14</v>
-      </c>
-      <c r="AW48" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2052,19 +2037,19 @@
       <c r="C49" t="s">
         <v>30</v>
       </c>
+      <c r="AP49" t="s">
+        <v>5</v>
+      </c>
       <c r="AQ49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AR49" t="s">
-        <v>9</v>
-      </c>
-      <c r="AS49" t="s">
         <v>26</v>
       </c>
+      <c r="AV49" t="s">
+        <v>14</v>
+      </c>
       <c r="AW49" t="s">
-        <v>14</v>
-      </c>
-      <c r="AX49" t="s">
         <v>20</v>
       </c>
     </row>
